--- a/output/pdf_financials_xlsx/LNF.xlsx
+++ b/output/pdf_financials_xlsx/LNF.xlsx
@@ -895,10 +895,10 @@
         <v>-0</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>-0</v>
+        <v>14.481</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>-0</v>
+        <v>10.502</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>-0</v>
@@ -910,16 +910,16 @@
         <v>-0</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>-0</v>
+        <v>-21.529</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-0</v>
+        <v>-19.458</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>-0</v>
+        <v>-14.437</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>-0</v>
+        <v>-12.864</v>
       </c>
     </row>
     <row r="14">
@@ -1515,10 +1515,10 @@
         <v>78.029</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>116.733</v>
+        <v>102.252</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>131.429</v>
+        <v>120.927</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>111.03</v>
@@ -1530,16 +1530,16 @@
         <v>270.612</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>240.707</v>
+        <v>262.236</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>191.2</v>
+        <v>210.658</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>213.287</v>
+        <v>227.724</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>219.44</v>
+        <v>232.304</v>
       </c>
     </row>
     <row r="28">
@@ -1595,10 +1595,10 @@
         <v>86.07299999999999</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>124.166</v>
+        <v>109.685</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>137.754</v>
+        <v>127.252</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>117.558</v>
@@ -1610,16 +1610,16 @@
         <v>272.422</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>242.177</v>
+        <v>263.706</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>192.252</v>
+        <v>211.71</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>214.484</v>
+        <v>228.921</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>220.531</v>
+        <v>233.395</v>
       </c>
     </row>
     <row r="30">
@@ -1635,10 +1635,10 @@
         <v>9.670993200091685</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>5.792037825553146</v>
+        <v>5.116534871831234</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>6.226968795090534</v>
+        <v>5.752241191637706</v>
       </c>
       <c r="F30" s="3" t="n">
         <v>12.03407597279491</v>
@@ -1650,16 +1650,16 @@
         <v>10.84193308313467</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>9.619134283078051</v>
+        <v>10.47425405902865</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>7.831711809039392</v>
+        <v>8.624366493413486</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>8.584356095247433</v>
+        <v>9.162172384327679</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>8.568556690616399</v>
+        <v>9.068377184189135</v>
       </c>
     </row>
     <row r="31">
@@ -4397,37 +4397,37 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>7.289</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>8.044</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>7.433</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>6.325</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>6.528</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>1.052</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>1.197</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>1.091</v>
       </c>
     </row>
     <row r="101">
@@ -15954,7 +15954,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -18465,7 +18465,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -22177,7 +22177,7 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E240" s="5" t="n">
@@ -27940,7 +27940,11 @@
           <t>Net finance costs 19</t>
         </is>
       </c>
-      <c r="D325" t="inlineStr"/>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E325" t="inlineStr">
         <is>
           <t>-</t>
@@ -38563,7 +38567,11 @@
           <t>Net finance costs (note 19)</t>
         </is>
       </c>
-      <c r="D480" t="inlineStr"/>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E480" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/LNF.xlsx
+++ b/output/pdf_financials_xlsx/LNF.xlsx
@@ -2664,7 +2664,7 @@
         <v>0</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>0</v>
+        <v>770.322</v>
       </c>
       <c r="E56" s="3" t="n">
         <v>0</v>
@@ -2704,7 +2704,7 @@
         <v>0</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>0</v>
+        <v>454.822</v>
       </c>
       <c r="E57" s="3" t="n">
         <v>0</v>
@@ -2993,7 +2993,7 @@
         <v>0</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>134.013</v>
       </c>
       <c r="H64" s="3" t="n">
         <v>543.737</v>
@@ -3153,7 +3153,7 @@
         <v>0</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0</v>
+        <v>134.013</v>
       </c>
       <c r="H68" s="3" t="n">
         <v>543.737</v>
@@ -3236,7 +3236,7 @@
         <v>0</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>0</v>
+        <v>74.92</v>
       </c>
       <c r="I70" s="3" t="n">
         <v>74.389</v>
@@ -3276,7 +3276,7 @@
         <v>0</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>90</v>
+        <v>164.92</v>
       </c>
       <c r="I71" s="3" t="n">
         <v>81.889</v>
@@ -3433,10 +3433,10 @@
         <v>607.52</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>570.968</v>
+        <v>436.955</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>566.0069999999999</v>
+        <v>491.087</v>
       </c>
       <c r="I75" s="3" t="n">
         <v>261.456</v>
@@ -3648,7 +3648,7 @@
         </is>
       </c>
       <c r="H80" s="3" t="n">
-        <v>0.4819734249418284</v>
+        <v>0.5766658704007745</v>
       </c>
       <c r="I80" s="3" t="n">
         <v>0.5998912674873639</v>
@@ -5043,10 +5043,10 @@
         <v>0</v>
       </c>
       <c r="D116" s="3" t="n">
-        <v>0</v>
+        <v>-0.6830000000000001</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>0</v>
+        <v>-1.164</v>
       </c>
       <c r="F116" s="3" t="n">
         <v>0</v>
@@ -5055,19 +5055,19 @@
         <v>0</v>
       </c>
       <c r="H116" s="3" t="n">
-        <v>0</v>
+        <v>-1.502</v>
       </c>
       <c r="I116" s="3" t="n">
-        <v>0</v>
+        <v>-1.038</v>
       </c>
       <c r="J116" s="3" t="n">
-        <v>0</v>
+        <v>-2.524</v>
       </c>
       <c r="K116" s="3" t="n">
-        <v>0</v>
+        <v>-0.673</v>
       </c>
       <c r="L116" s="3" t="n">
-        <v>0</v>
+        <v>-0.314</v>
       </c>
     </row>
     <row r="117">
@@ -5255,10 +5255,10 @@
         <v>0</v>
       </c>
       <c r="H121" s="3" t="n">
-        <v>0</v>
+        <v>-64.574</v>
       </c>
       <c r="I121" s="3" t="n">
-        <v>0</v>
+        <v>-244.274</v>
       </c>
       <c r="J121" s="3" t="n">
         <v>0</v>
@@ -5267,7 +5267,7 @@
         <v>0</v>
       </c>
       <c r="L121" s="3" t="n">
-        <v>0</v>
+        <v>-0.9350000000000001</v>
       </c>
     </row>
     <row r="122">
@@ -10183,7 +10183,11 @@
           <t>Lease liabilities 13</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
           <t>-</t>
@@ -17141,7 +17145,11 @@
           <t>Purchase of intangible assets 10</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr"/>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E166" t="inlineStr">
         <is>
           <t>-</t>
@@ -17787,7 +17795,11 @@
           <t>Repurchase of common shares 16</t>
         </is>
       </c>
-      <c r="D176" t="inlineStr"/>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E176" t="inlineStr">
         <is>
           <t>-</t>
@@ -20231,7 +20243,11 @@
           <t>Decrease of employee loans-redeemable shares 2,239 611 REPORTRepurchase of common shares 16</t>
         </is>
       </c>
-      <c r="D212" t="inlineStr"/>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E212" t="inlineStr">
         <is>
           <t>-</t>
@@ -26032,7 +26048,11 @@
           <t>Purchase of intangible assets (note 10)</t>
         </is>
       </c>
-      <c r="D297" t="inlineStr"/>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E297" t="inlineStr">
         <is>
           <t>-</t>
